--- a/04_DESIGN_TABLES/DesignTable_6809.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6809.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1524,6 +1529,252 @@
       <c r="S18" t="inlineStr">
         <is>
           <t>6809-20-20-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6809-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6809-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7/16-20 (B (1) UN/UNF-2A) x 7/16-20 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / hexes / flats / bores from the Brennan TFA catalog p.44; ORB / JIC majors from the end libraries</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6809-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6809-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6809-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>9/16-18 (B (1) UN/UNF-2A) x 9/16-18 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / hexes / flats / bores from the Brennan TFA catalog p.44; ORB / JIC majors from the end libraries</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6809-06-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6809-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6809-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3/4-16 (B (1) UN/UNF-2A) x 3/4-16 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / hexes / flats / bores from the Brennan TFA catalog p.44; ORB / JIC majors from the end libraries</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.44 alone; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>6809-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
